--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118745328</v>
+        <v>118745231</v>
       </c>
       <c r="B2" t="n">
-        <v>80441</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388075</v>
+        <v>387995</v>
       </c>
       <c r="R2" t="n">
-        <v>6612044</v>
+        <v>6611997</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,26 +775,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118745231</v>
+        <v>118745328</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>80441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,48 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387995</v>
+        <v>388075</v>
       </c>
       <c r="R3" t="n">
-        <v>6611997</v>
+        <v>6612044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,6 +877,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118745231</v>
+        <v>118745328</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>80441</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,48 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387995</v>
+        <v>388075</v>
       </c>
       <c r="R2" t="n">
-        <v>6611997</v>
+        <v>6612044</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,6 +761,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118745328</v>
+        <v>118745231</v>
       </c>
       <c r="B3" t="n">
-        <v>80441</v>
+        <v>57306</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,34 +813,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388075</v>
+        <v>387995</v>
       </c>
       <c r="R3" t="n">
-        <v>6612044</v>
+        <v>6611997</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,26 +897,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118745328</v>
       </c>
       <c r="B2" t="n">
-        <v>80441</v>
+        <v>80448</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118745328</v>
+        <v>118745231</v>
       </c>
       <c r="B2" t="n">
-        <v>80448</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>388075</v>
+        <v>387995</v>
       </c>
       <c r="R2" t="n">
-        <v>6612044</v>
+        <v>6611997</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,26 +775,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -797,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118745231</v>
+        <v>118745328</v>
       </c>
       <c r="B3" t="n">
-        <v>57306</v>
+        <v>80448</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,48 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Glansbergen (Glansbergen), Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>387995</v>
+        <v>388075</v>
       </c>
       <c r="R3" t="n">
-        <v>6611997</v>
+        <v>6612044</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,6 +877,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>122787019</v>
       </c>
       <c r="B4" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,6 +1044,210 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123460611</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96903</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>388033</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6612069</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123459111</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78771</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>388061</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6611975</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1049,7 +1049,7 @@
         <v>123460611</v>
       </c>
       <c r="B5" t="n">
-        <v>96903</v>
+        <v>96909</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>123459111</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>122787019</v>
       </c>
       <c r="B4" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>123460611</v>
       </c>
       <c r="B5" t="n">
-        <v>96912</v>
+        <v>96929</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>123459111</v>
       </c>
       <c r="B6" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -916,7 +916,7 @@
         <v>122787019</v>
       </c>
       <c r="B4" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>123460611</v>
       </c>
       <c r="B5" t="n">
-        <v>96929</v>
+        <v>96945</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>123459111</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123460611</v>
+        <v>123459111</v>
       </c>
       <c r="B5" t="n">
-        <v>96945</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,25 +1058,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388033</v>
+        <v>388061</v>
       </c>
       <c r="R5" t="n">
-        <v>6612069</v>
+        <v>6611975</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123459111</v>
+        <v>123460611</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>96947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,25 +1160,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388061</v>
+        <v>388033</v>
       </c>
       <c r="R6" t="n">
-        <v>6611975</v>
+        <v>6612069</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1151,7 +1151,7 @@
         <v>123460611</v>
       </c>
       <c r="B6" t="n">
-        <v>96947</v>
+        <v>96707</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123459111</v>
+        <v>123460611</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>96707</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,25 +1058,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388061</v>
+        <v>388033</v>
       </c>
       <c r="R5" t="n">
-        <v>6611975</v>
+        <v>6612069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123460611</v>
+        <v>123459111</v>
       </c>
       <c r="B6" t="n">
-        <v>96707</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,25 +1160,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388033</v>
+        <v>388061</v>
       </c>
       <c r="R6" t="n">
-        <v>6612069</v>
+        <v>6611975</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1046,10 +1046,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123460611</v>
+        <v>123459111</v>
       </c>
       <c r="B5" t="n">
-        <v>96707</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1058,25 +1058,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1086,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388033</v>
+        <v>388061</v>
       </c>
       <c r="R5" t="n">
-        <v>6612069</v>
+        <v>6611975</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123459111</v>
+        <v>123460611</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>96707</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,25 +1160,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388061</v>
+        <v>388033</v>
       </c>
       <c r="R6" t="n">
-        <v>6611975</v>
+        <v>6612069</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,6 +1248,128 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125543869</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57635</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>388057</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6612103</v>
+      </c>
+      <c r="S7" t="n">
+        <v>8</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1370,6 +1370,327 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125684857</v>
+      </c>
+      <c r="B8" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>388104</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6612105</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>125684772</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96897</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>388038</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6612070</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125684774</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>388074</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6611982</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1253,12 +1253,7 @@
         <v>125543869</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1372,15 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684857</v>
+        <v>125684774</v>
       </c>
       <c r="B8" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388104</v>
+        <v>388074</v>
       </c>
       <c r="R8" t="n">
-        <v>6612105</v>
+        <v>6611982</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1442,12 +1432,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1479,37 +1469,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684772</v>
+        <v>125684857</v>
       </c>
       <c r="B9" t="n">
-        <v>96897</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2569</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388038</v>
+        <v>388104</v>
       </c>
       <c r="R9" t="n">
-        <v>6612070</v>
+        <v>6612105</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1549,12 +1534,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1586,37 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125684774</v>
+        <v>125684772</v>
       </c>
       <c r="B10" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96952</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388074</v>
+        <v>388038</v>
       </c>
       <c r="R10" t="n">
-        <v>6611982</v>
+        <v>6612070</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>125684857</v>
       </c>
       <c r="B9" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125684772</v>
       </c>
       <c r="B10" t="n">
-        <v>96952</v>
+        <v>96959</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>125684774</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125684857</v>
       </c>
       <c r="B9" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125684772</v>
       </c>
       <c r="B10" t="n">
-        <v>96959</v>
+        <v>96962</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>125684774</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125684857</v>
       </c>
       <c r="B9" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125684772</v>
       </c>
       <c r="B10" t="n">
-        <v>96962</v>
+        <v>96966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>125684857</v>
       </c>
       <c r="B9" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125684772</v>
       </c>
       <c r="B10" t="n">
-        <v>96966</v>
+        <v>96967</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1253,7 +1253,7 @@
         <v>125543869</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>125684774</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125684857</v>
       </c>
       <c r="B9" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125684772</v>
       </c>
       <c r="B10" t="n">
-        <v>96967</v>
+        <v>96969</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>125684857</v>
       </c>
       <c r="B9" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125684772</v>
       </c>
       <c r="B10" t="n">
-        <v>96969</v>
+        <v>96971</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>125684857</v>
       </c>
       <c r="B9" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125684772</v>
       </c>
       <c r="B10" t="n">
-        <v>96971</v>
+        <v>96973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1370,7 +1370,7 @@
         <v>125684774</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>125684857</v>
       </c>
       <c r="B9" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125684772</v>
       </c>
       <c r="B10" t="n">
-        <v>96973</v>
+        <v>96977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -1472,7 +1472,7 @@
         <v>125684857</v>
       </c>
       <c r="B9" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>125684772</v>
       </c>
       <c r="B10" t="n">
-        <v>96977</v>
+        <v>96980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118745231</v>
+        <v>125684857</v>
       </c>
       <c r="B2" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,51 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Glansbergen (Glansbergen), Vrm</t>
+          <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>387995</v>
+        <v>388104</v>
       </c>
       <c r="R2" t="n">
-        <v>6611997</v>
+        <v>6612105</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-09-02</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,27 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118745328</v>
+        <v>127272827</v>
       </c>
       <c r="B3" t="n">
-        <v>80450</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92640</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,34 +788,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>757</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Apelsinticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Hapalopilus aurantiacus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Rostk.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Glansbergen (Glansbergen), Vrm</t>
+          <t>Stockbergen, Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>388075</v>
+        <v>388084</v>
       </c>
       <c r="R3" t="n">
-        <v>6612044</v>
+        <v>6611936</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +845,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,107 +869,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Lina Lejonberg, Alexander Singer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122787019</v>
+        <v>118745328</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Glansbergen,Brunskog, Vrm, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388070</v>
+        <v>388075</v>
       </c>
       <c r="R4" t="n">
-        <v>6611997</v>
+        <v>6612044</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,27 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:13</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>30 Färsk spillning under tall.</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,53 +969,68 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sara Poppelaars</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123459111</v>
+        <v>123460611</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1086,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388061</v>
+        <v>388033</v>
       </c>
       <c r="R5" t="n">
-        <v>6611975</v>
+        <v>6612069</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,15 +1102,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123460611</v>
+        <v>125684772</v>
       </c>
       <c r="B6" t="n">
-        <v>96729</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,17 +1133,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Stockbergen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388033</v>
+        <v>388038</v>
       </c>
       <c r="R6" t="n">
-        <v>6612069</v>
+        <v>6612070</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,6 +1173,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,65 +1192,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Lina Lejonberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125543869</v>
+        <v>123466722</v>
       </c>
       <c r="B7" t="n">
-        <v>57652</v>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>388057</v>
+        <v>387971</v>
       </c>
       <c r="R7" t="n">
-        <v>6612103</v>
+        <v>6612005</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,27 +1269,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,26 +1289,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jesper Granback</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125684774</v>
+        <v>118745145</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1398,17 +1332,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>388074</v>
+        <v>387990</v>
       </c>
       <c r="R8" t="n">
-        <v>6611982</v>
+        <v>6611950</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,17 +1366,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,64 +1382,84 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125684857</v>
+        <v>123459111</v>
       </c>
       <c r="B9" t="n">
-        <v>96605</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>388104</v>
+        <v>388061</v>
       </c>
       <c r="R9" t="n">
-        <v>6612105</v>
+        <v>6611975</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,17 +1483,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,60 +1503,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lina Lejonberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125684772</v>
+        <v>123464304</v>
       </c>
       <c r="B10" t="n">
-        <v>96980</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2569</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stockbergen, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>388038</v>
+        <v>387976</v>
       </c>
       <c r="R10" t="n">
-        <v>6612070</v>
+        <v>6612015</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1639,14 +1583,19 @@
           <t>2025-03-25</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-25</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Stockbergen</t>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,6 +1619,1083 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123468945</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>387976</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6611967</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>125684774</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>388074</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6611982</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125684771</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stockbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>387969</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6611987</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Stockbergen</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lina Lejonberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>118745231</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>387995</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6611997</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-07-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125543869</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>388057</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6612103</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122787019</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Glansbergen,Brunskog, Vrm, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>388070</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6611997</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>30 Färsk spillning under tall.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sara Poppelaars</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123465823</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>387973</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6612012</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123465746</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>387975</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6612015</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123466234</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>387972</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6612010</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123468569</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>387975</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6611968</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123465823</v>
+        <v>135897887</v>
       </c>
       <c r="B17" t="n">
-        <v>57132</v>
+        <v>57167</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,42 +2370,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387973</v>
+        <v>388003</v>
       </c>
       <c r="R17" t="n">
-        <v>6612012</v>
+        <v>6611987</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2429,12 +2428,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>00:46</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder från tjäder upphittad på marken samtidigt som tjäder flög förbi vid trädtopparna</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,59 +2463,55 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465823</t>
+          <t>https://artportalen.se/Sighting/135897887</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123465746</v>
+        <v>123465823</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2510,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387975</v>
+        <v>387973</v>
       </c>
       <c r="R18" t="n">
-        <v>6612015</v>
+        <v>6612012</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,13 +2581,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465746</t>
+          <t>https://artportalen.se/Sighting/123465823</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123466234</v>
+        <v>123465746</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2607,7 +2617,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2621,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387972</v>
+        <v>387975</v>
       </c>
       <c r="R19" t="n">
-        <v>6612010</v>
+        <v>6612015</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,13 +2692,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123466234</t>
+          <t>https://artportalen.se/Sighting/123465746</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123468569</v>
+        <v>123466234</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2718,7 +2728,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2732,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387975</v>
+        <v>387972</v>
       </c>
       <c r="R20" t="n">
-        <v>6611968</v>
+        <v>6612010</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2792,6 +2802,117 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123466234</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123468569</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>387975</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6611968</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123468569</t>
         </is>
@@ -2818,6 +2939,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135897887</v>
+        <v>123465823</v>
       </c>
       <c r="B17" t="n">
-        <v>57167</v>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,41 +2370,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Glansbergen, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388003</v>
+        <v>387973</v>
       </c>
       <c r="R17" t="n">
-        <v>6611987</v>
+        <v>6612012</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2428,27 +2429,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:46</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:46</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder från tjäder upphittad på marken samtidigt som tjäder flög förbi vid trädtopparna</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,55 +2449,59 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135897887</t>
+          <t>https://artportalen.se/Sighting/123465823</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123465823</v>
+        <v>123465746</v>
       </c>
       <c r="B18" t="n">
-        <v>57132</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2520,10 +2510,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387973</v>
+        <v>387975</v>
       </c>
       <c r="R18" t="n">
-        <v>6612012</v>
+        <v>6612015</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,13 +2571,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465823</t>
+          <t>https://artportalen.se/Sighting/123465746</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123465746</v>
+        <v>123466234</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2617,7 +2607,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2631,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387975</v>
+        <v>387972</v>
       </c>
       <c r="R19" t="n">
-        <v>6612015</v>
+        <v>6612010</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,13 +2682,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465746</t>
+          <t>https://artportalen.se/Sighting/123466234</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123466234</v>
+        <v>123468569</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2728,7 +2718,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2742,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387972</v>
+        <v>387975</v>
       </c>
       <c r="R20" t="n">
-        <v>6612010</v>
+        <v>6611968</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,117 +2792,6 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/123466234</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>123468569</v>
-      </c>
-      <c r="B21" t="n">
-        <v>99118</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>387975</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6611968</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123468569</t>
         </is>
@@ -2939,7 +2818,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -2362,7 +2362,7 @@
         <v>135897887</v>
       </c>
       <c r="B17" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135897887</v>
+        <v>123465823</v>
       </c>
       <c r="B17" t="n">
-        <v>57169</v>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,41 +2370,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Glansbergen, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388003</v>
+        <v>387973</v>
       </c>
       <c r="R17" t="n">
-        <v>6611987</v>
+        <v>6612012</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2428,27 +2429,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:46</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:46</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder från tjäder upphittad på marken samtidigt som tjäder flög förbi vid trädtopparna</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,55 +2449,59 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135897887</t>
+          <t>https://artportalen.se/Sighting/123465823</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123465823</v>
+        <v>123465746</v>
       </c>
       <c r="B18" t="n">
-        <v>57132</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2520,10 +2510,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387973</v>
+        <v>387975</v>
       </c>
       <c r="R18" t="n">
-        <v>6612012</v>
+        <v>6612015</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,13 +2571,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465823</t>
+          <t>https://artportalen.se/Sighting/123465746</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123465746</v>
+        <v>123466234</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2617,7 +2607,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2631,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387975</v>
+        <v>387972</v>
       </c>
       <c r="R19" t="n">
-        <v>6612015</v>
+        <v>6612010</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,13 +2682,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465746</t>
+          <t>https://artportalen.se/Sighting/123466234</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123466234</v>
+        <v>123468569</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2728,7 +2718,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2742,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387972</v>
+        <v>387975</v>
       </c>
       <c r="R20" t="n">
-        <v>6612010</v>
+        <v>6611968</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,117 +2792,6 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/123466234</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>123468569</v>
-      </c>
-      <c r="B21" t="n">
-        <v>99118</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>387975</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6611968</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123468569</t>
         </is>
@@ -2939,7 +2818,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123465823</v>
+        <v>135897887</v>
       </c>
       <c r="B17" t="n">
-        <v>57132</v>
+        <v>57169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,42 +2370,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387973</v>
+        <v>388003</v>
       </c>
       <c r="R17" t="n">
-        <v>6612012</v>
+        <v>6611987</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2429,12 +2428,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>00:46</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder från tjäder upphittad på marken samtidigt som tjäder flög förbi vid trädtopparna</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,59 +2463,55 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465823</t>
+          <t>https://artportalen.se/Sighting/135897887</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123465746</v>
+        <v>123465823</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2510,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387975</v>
+        <v>387973</v>
       </c>
       <c r="R18" t="n">
-        <v>6612015</v>
+        <v>6612012</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,13 +2581,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465746</t>
+          <t>https://artportalen.se/Sighting/123465823</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123466234</v>
+        <v>123465746</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2607,7 +2617,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2621,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387972</v>
+        <v>387975</v>
       </c>
       <c r="R19" t="n">
-        <v>6612010</v>
+        <v>6612015</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,13 +2692,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123466234</t>
+          <t>https://artportalen.se/Sighting/123465746</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123468569</v>
+        <v>123466234</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2718,7 +2728,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2732,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387975</v>
+        <v>387972</v>
       </c>
       <c r="R20" t="n">
-        <v>6611968</v>
+        <v>6612010</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2792,6 +2802,117 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123466234</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123468569</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>387975</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6611968</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123468569</t>
         </is>
@@ -2818,6 +2939,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -2362,7 +2362,7 @@
         <v>135897887</v>
       </c>
       <c r="B17" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -2362,7 +2362,7 @@
         <v>135897887</v>
       </c>
       <c r="B17" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -2362,7 +2362,7 @@
         <v>135897887</v>
       </c>
       <c r="B17" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -2362,7 +2362,7 @@
         <v>135897887</v>
       </c>
       <c r="B17" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135897887</v>
+        <v>123465823</v>
       </c>
       <c r="B17" t="n">
-        <v>57180</v>
+        <v>57132</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,41 +2370,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Glansbergen, Vrm</t>
+          <t>Glansbergen, Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>388003</v>
+        <v>387973</v>
       </c>
       <c r="R17" t="n">
-        <v>6611987</v>
+        <v>6612012</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2428,27 +2429,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:46</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:46</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Fjäder från tjäder upphittad på marken samtidigt som tjäder flög förbi vid trädtopparna</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2463,55 +2449,59 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135897887</t>
+          <t>https://artportalen.se/Sighting/123465823</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123465823</v>
+        <v>123465746</v>
       </c>
       <c r="B18" t="n">
-        <v>57132</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2520,10 +2510,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387973</v>
+        <v>387975</v>
       </c>
       <c r="R18" t="n">
-        <v>6612012</v>
+        <v>6612015</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2581,13 +2571,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465823</t>
+          <t>https://artportalen.se/Sighting/123465746</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123465746</v>
+        <v>123466234</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2617,7 +2607,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2631,10 +2621,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387975</v>
+        <v>387972</v>
       </c>
       <c r="R19" t="n">
-        <v>6612015</v>
+        <v>6612010</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2692,13 +2682,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465746</t>
+          <t>https://artportalen.se/Sighting/123466234</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123466234</v>
+        <v>123468569</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2728,7 +2718,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2742,10 +2732,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387972</v>
+        <v>387975</v>
       </c>
       <c r="R20" t="n">
-        <v>6612010</v>
+        <v>6611968</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,117 +2792,6 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/123466234</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>123468569</v>
-      </c>
-      <c r="B21" t="n">
-        <v>99118</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>387975</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6611968</v>
-      </c>
-      <c r="S21" t="n">
-        <v>10</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Arvika</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Värmland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Brunskog</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2025-03-25</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Alexander Singer</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123468569</t>
         </is>
@@ -2939,7 +2818,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21224-2024 artfynd.xlsx
+++ b/artfynd/A 21224-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123465823</v>
+        <v>135897887</v>
       </c>
       <c r="B17" t="n">
-        <v>57132</v>
+        <v>57193</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2370,42 +2370,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Glansbergen, Glansbergen, Vrm</t>
+          <t>Glansbergen, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>387973</v>
+        <v>388003</v>
       </c>
       <c r="R17" t="n">
-        <v>6612012</v>
+        <v>6611987</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2429,12 +2428,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>00:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>00:46</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Fjäder från tjäder upphittad på marken samtidigt som tjäder flög förbi vid trädtopparna</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2449,59 +2463,55 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465823</t>
+          <t>https://artportalen.se/Sighting/135897887</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123465746</v>
+        <v>123465823</v>
       </c>
       <c r="B18" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2510,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>387975</v>
+        <v>387973</v>
       </c>
       <c r="R18" t="n">
-        <v>6612015</v>
+        <v>6612012</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2571,13 +2581,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123465746</t>
+          <t>https://artportalen.se/Sighting/123465823</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123466234</v>
+        <v>123465746</v>
       </c>
       <c r="B19" t="n">
         <v>99118</v>
@@ -2607,7 +2617,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>83</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2621,10 +2631,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>387972</v>
+        <v>387975</v>
       </c>
       <c r="R19" t="n">
-        <v>6612010</v>
+        <v>6612015</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2682,13 +2692,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123466234</t>
+          <t>https://artportalen.se/Sighting/123465746</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123468569</v>
+        <v>123466234</v>
       </c>
       <c r="B20" t="n">
         <v>99118</v>
@@ -2718,7 +2728,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2732,10 +2742,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>387975</v>
+        <v>387972</v>
       </c>
       <c r="R20" t="n">
-        <v>6611968</v>
+        <v>6612010</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2792,6 +2802,117 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123466234</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123468569</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Glansbergen, Glansbergen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>387975</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6611968</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/123468569</t>
         </is>
@@ -2818,6 +2939,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
